--- a/data/trans_orig/P32A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32A-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2007</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134739</t>
+          <t>135629</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145137</t>
+          <t>144261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71494</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73476</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208974</t>
+          <t>208381</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217727</t>
+          <t>217734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11462</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>218075</t>
+          <t>217379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226772</t>
+          <t>226775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70842</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72751</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>290106</t>
+          <t>290004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,62 +1454,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5920</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5782</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188710</t>
+          <t>187558</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84096</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>274127</t>
+          <t>273989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231939</t>
+          <t>231012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125986</t>
+          <t>124171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>361027</t>
+          <t>360806</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367907</t>
+          <t>367895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,62 +2140,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6095</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5266</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92387</t>
+          <t>92597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45287</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47296</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138928</t>
+          <t>138099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,62 +2483,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1733</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>8664</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184241</t>
+          <t>184789</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108796</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>296382</t>
+          <t>295322</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,62 +2826,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1836</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5566</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1836</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6650</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>284307</t>
+          <t>283475</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130458</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132381</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>415764</t>
+          <t>416848</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9711</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>485263</t>
+          <t>485391</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>492117</t>
+          <t>492111</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>233120</t>
+          <t>233688</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>723115</t>
+          <t>722637</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>920</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15277</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34160</t>
+          <t>35166</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1849926</t>
+          <t>1850945</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1868000</t>
+          <t>1868939</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>885575</t>
+          <t>885511</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>892575</t>
+          <t>892579</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2740243</t>
+          <t>2739237</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2759218</t>
+          <t>2759126</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2012</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2012 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>15737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>33582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18688</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38877</t>
+          <t>39720</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143116</t>
+          <t>141743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160771</t>
+          <t>159588</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97919</t>
+          <t>96018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108492</t>
+          <t>107867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246140</t>
+          <t>245297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>266329</t>
+          <t>266682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>295894</t>
+          <t>295035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>308121</t>
+          <t>308081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>145341</t>
+          <t>146052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>445977</t>
+          <t>445201</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>458556</t>
+          <t>458533</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,62 +4777,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2078</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4694</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5373</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>196662</t>
+          <t>196517</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121506</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123584</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319656</t>
+          <t>320335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,62 +5120,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1891</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6722</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5791</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>185243</t>
+          <t>184383</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85350</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87342</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>272580</t>
+          <t>271649</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>116121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>126248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49044</t>
+          <t>48922</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>169933</t>
+          <t>169286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>180134</t>
+          <t>179480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176477</t>
+          <t>177410</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90083</t>
+          <t>90177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>271741</t>
+          <t>270834</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17666</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19506</t>
+          <t>19922</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>376988</t>
+          <t>376748</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>390622</t>
+          <t>390740</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>206254</t>
+          <t>206079</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>586365</t>
+          <t>585949</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>600714</t>
+          <t>600888</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16040</t>
+          <t>15041</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>436886</t>
+          <t>437569</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>450227</t>
+          <t>450765</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>209823</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>211908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>648681</t>
+          <t>649680</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>662659</t>
+          <t>662651</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37804</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69413</t>
+          <t>69394</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44321</t>
+          <t>45046</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>79962</t>
+          <t>78254</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1965967</t>
+          <t>1965986</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1997576</t>
+          <t>1997200</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1026850</t>
+          <t>1026322</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1040431</t>
+          <t>1040374</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2999865</t>
+          <t>3001573</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3035506</t>
+          <t>3034781</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2016</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23022</t>
+          <t>23394</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161870</t>
+          <t>161415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>174493</t>
+          <t>174684</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94377</t>
+          <t>95210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105222</t>
+          <t>105229</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>261811</t>
+          <t>261439</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>277548</t>
+          <t>278082</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>254455</t>
+          <t>254724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>265512</t>
+          <t>265511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95950</t>
+          <t>95742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>353496</t>
+          <t>355562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>366686</t>
+          <t>366775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,47 +8100,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1850</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200127</t>
+          <t>199941</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119726</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121576</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>322339</t>
+          <t>322355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,62 +8443,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2064</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5175</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6955</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227069</t>
+          <t>227098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150733</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152797</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>379251</t>
+          <t>381031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83342</t>
+          <t>83707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90253</t>
+          <t>90258</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120976</t>
+          <t>120825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127727</t>
+          <t>127724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180849</t>
+          <t>180959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188161</t>
+          <t>188168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>99115</t>
+          <t>98154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>283461</t>
+          <t>282724</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>292825</t>
+          <t>292786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>26238</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>30497</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>355710</t>
+          <t>353534</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>371826</t>
+          <t>371078</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>244705</t>
+          <t>244568</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>254272</t>
+          <t>254179</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>606557</t>
+          <t>604663</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>623914</t>
+          <t>623117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>449818</t>
+          <t>449853</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>253837</t>
+          <t>254324</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>262981</t>
+          <t>262997</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>708276</t>
+          <t>707879</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>718410</t>
+          <t>718343</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27273</t>
+          <t>28847</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54016</t>
+          <t>55342</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26333</t>
+          <t>24966</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>41469</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>70542</t>
+          <t>71005</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1947346</t>
+          <t>1946020</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1974089</t>
+          <t>1972515</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1118979</t>
+          <t>1120346</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1136729</t>
+          <t>1136498</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3076132</t>
+          <t>3075669</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3105205</t>
+          <t>3105519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2023</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2023 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,62 +10737,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>9423</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2315</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>10938</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169847</t>
+          <t>172108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89622</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>259634</t>
+          <t>261149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,62 +11080,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1509</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>7175</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7076</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243493</t>
+          <t>242267</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107898</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109407</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>352681</t>
+          <t>352582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>14396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172906</t>
+          <t>171691</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181637</t>
+          <t>181514</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86780</t>
+          <t>86593</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>260677</t>
+          <t>261062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270924</t>
+          <t>270674</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>482</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170627</t>
+          <t>170707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>176760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119555</t>
+          <t>119785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123923</t>
+          <t>123863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>293092</t>
+          <t>293093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>300008</t>
+          <t>300199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -12074,97 +12074,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>23,83%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>440</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2437</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37292</t>
+          <t>37239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154805</t>
+          <t>154708</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162766</t>
+          <t>162919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90595</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95894</t>
+          <t>95868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>248636</t>
+          <t>249052</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258013</t>
+          <t>258208</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>20734</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>25833</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>294899</t>
+          <t>294067</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>305116</t>
+          <t>304706</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>378214</t>
+          <t>378899</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>398653</t>
+          <t>398234</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>680110</t>
+          <t>681730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>701787</t>
+          <t>702323</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>268739</t>
+          <t>268974</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275864</t>
+          <t>275818</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>94562</t>
+          <t>95275</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>366701</t>
+          <t>367691</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>374599</t>
+          <t>374591</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38761</t>
+          <t>39309</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29711</t>
+          <t>28537</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56615</t>
+          <t>55541</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1534776</t>
+          <t>1534228</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1553617</t>
+          <t>1554131</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>993982</t>
+          <t>994306</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1012236</t>
+          <t>1012417</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2535366</t>
+          <t>2536440</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2562270</t>
+          <t>2563444</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32A-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135629</t>
+          <t>135332</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144261</t>
+          <t>144240</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208381</t>
+          <t>208913</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217734</t>
+          <t>217714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217379</t>
+          <t>216132</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226775</t>
+          <t>226760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>290004</t>
+          <t>290028</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>299524</t>
+          <t>299505</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>187558</t>
+          <t>188095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>273989</t>
+          <t>274607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231012</t>
+          <t>231814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124171</t>
+          <t>126247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360806</t>
+          <t>361447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367895</t>
+          <t>367907</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92597</t>
+          <t>92785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138099</t>
+          <t>139735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184789</t>
+          <t>184995</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>295322</t>
+          <t>297053</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>283475</t>
+          <t>283587</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>416848</t>
+          <t>416727</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>485391</t>
+          <t>485919</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>492111</t>
+          <t>492112</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>233688</t>
+          <t>232774</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>722637</t>
+          <t>723245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>731055</t>
+          <t>731084</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>29693</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35166</t>
+          <t>35509</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1850945</t>
+          <t>1851211</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1868939</t>
+          <t>1868558</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>885511</t>
+          <t>885493</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>892579</t>
+          <t>892575</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2739237</t>
+          <t>2738894</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2759126</t>
+          <t>2759023</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>15459</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>34202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39720</t>
+          <t>38736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141743</t>
+          <t>141123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159588</t>
+          <t>159866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96018</t>
+          <t>97801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107867</t>
+          <t>108475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>245297</t>
+          <t>246281</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>266682</t>
+          <t>266079</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>295035</t>
+          <t>295967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>308081</t>
+          <t>308122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146052</t>
+          <t>146012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>445201</t>
+          <t>445933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>458533</t>
+          <t>458554</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>196517</t>
+          <t>196875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320335</t>
+          <t>319214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184383</t>
+          <t>185117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>271649</t>
+          <t>272202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>116121</t>
+          <t>115196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126248</t>
+          <t>126273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48922</t>
+          <t>49581</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>169286</t>
+          <t>170059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>179480</t>
+          <t>180334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177410</t>
+          <t>177056</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90177</t>
+          <t>89875</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>270834</t>
+          <t>270835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17906</t>
+          <t>17914</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19922</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>376748</t>
+          <t>376740</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>390740</t>
+          <t>390805</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>206079</t>
+          <t>205471</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>585949</t>
+          <t>585861</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>600888</t>
+          <t>600746</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>15581</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>437569</t>
+          <t>435615</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>450765</t>
+          <t>450760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>649680</t>
+          <t>649140</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>662651</t>
+          <t>662687</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>39128</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69394</t>
+          <t>70569</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>17226</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>45046</t>
+          <t>46237</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>78254</t>
+          <t>80252</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1965986</t>
+          <t>1964811</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1997200</t>
+          <t>1996252</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1026322</t>
+          <t>1027220</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1040374</t>
+          <t>1040624</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3001573</t>
+          <t>2999575</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3034781</t>
+          <t>3033590</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>18240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23394</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161415</t>
+          <t>160432</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>174684</t>
+          <t>174416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95210</t>
+          <t>95414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105229</t>
+          <t>105231</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>261439</t>
+          <t>262172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>278082</t>
+          <t>277960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14435</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>254724</t>
+          <t>253915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>265511</t>
+          <t>265510</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95742</t>
+          <t>97749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>355562</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>366775</t>
+          <t>366703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>199941</t>
+          <t>200352</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>322355</t>
+          <t>321831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227098</t>
+          <t>227026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>381031</t>
+          <t>377964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83707</t>
+          <t>83624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90258</t>
+          <t>90243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120825</t>
+          <t>120015</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127724</t>
+          <t>127718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180959</t>
+          <t>182543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188168</t>
+          <t>188163</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98154</t>
+          <t>97808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>282724</t>
+          <t>284078</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>292786</t>
+          <t>292821</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26238</t>
+          <t>25331</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10820</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30497</t>
+          <t>29306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>353534</t>
+          <t>354441</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>371078</t>
+          <t>371725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>244568</t>
+          <t>244877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>254179</t>
+          <t>254271</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>604663</t>
+          <t>605854</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>623117</t>
+          <t>624334</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>449853</t>
+          <t>449612</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>254324</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>262997</t>
+          <t>263073</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>707879</t>
+          <t>707658</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>718343</t>
+          <t>718383</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>27913</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55342</t>
+          <t>53413</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24966</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>40566</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>71005</t>
+          <t>71659</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1946020</t>
+          <t>1947949</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1972515</t>
+          <t>1973449</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1120346</t>
+          <t>1120552</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1136498</t>
+          <t>1136949</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3075669</t>
+          <t>3075015</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3105519</t>
+          <t>3106108</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -10707,12 +10707,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -10810,27 +10810,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>177574</t>
+          <t>167944</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172108</t>
+          <t>162800</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -10880,27 +10880,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>268257</t>
+          <t>265175</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>261149</t>
+          <t>260791</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -11153,27 +11153,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>249030</t>
+          <t>252048</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>242267</t>
+          <t>246100</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>109407</t>
+          <t>115337</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11223,17 +11223,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>358437</t>
+          <t>367385</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>352582</t>
+          <t>360984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359757</t>
+          <t>368766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>109407</t>
+          <t>115337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109407</t>
+          <t>115337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>109407</t>
+          <t>115337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>359757</t>
+          <t>368766</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>359757</t>
+          <t>368766</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>359757</t>
+          <t>368766</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -11428,12 +11428,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>177789</t>
+          <t>179342</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171691</t>
+          <t>173243</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181514</t>
+          <t>183147</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,27 +11531,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89221</t>
+          <t>88142</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86593</t>
+          <t>85725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>267010</t>
+          <t>267483</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>261062</t>
+          <t>261201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270674</t>
+          <t>271402</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>453</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>174979</t>
+          <t>200212</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170707</t>
+          <t>195597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176760</t>
+          <t>201961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>122620</t>
+          <t>136521</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119785</t>
+          <t>133647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123863</t>
+          <t>137913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>297599</t>
+          <t>336734</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>293093</t>
+          <t>331753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>300199</t>
+          <t>339242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,27 +12252,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>44513</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>160072</t>
+          <t>158239</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154708</t>
+          <t>153445</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162919</t>
+          <t>161136</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>94204</t>
+          <t>95963</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>91981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95868</t>
+          <t>97648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>254276</t>
+          <t>254201</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249052</t>
+          <t>248731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258208</t>
+          <t>257683</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,102 +12755,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>12956</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>6712</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>23831</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>21891</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>12866</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>34251</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>2,2%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>7965</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>20734</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>14753</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>5240</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>25833</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -12868,102 +12868,102 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>301142</t>
+          <t>340770</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>294067</t>
+          <t>333272</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>304706</t>
+          <t>345682</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>95,3%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>221401</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>210526</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>227645</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>94,47%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>97,14%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>562171</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>549811</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>571196</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>94,14%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>97,8%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>95,5%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>391668</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>378899</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>398234</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>94,81%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>692810</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>681730</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>702323</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>399633</t>
+          <t>234357</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>399633</t>
+          <t>234357</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>399633</t>
+          <t>234357</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707563</t>
+          <t>584062</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707563</t>
+          <t>584062</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707563</t>
+          <t>584062</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -13143,12 +13143,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>804</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>273817</t>
+          <t>310176</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>268974</t>
+          <t>304714</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275818</t>
+          <t>312469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,27 +13246,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>98402</t>
+          <t>113362</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95275</t>
+          <t>110345</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>372218</t>
+          <t>423538</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>367691</t>
+          <t>418117</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>374591</t>
+          <t>426557</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>27988</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>21105</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39309</t>
+          <t>42024</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24138</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>49810</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28537</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>55541</t>
+          <t>65653</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1545549</t>
+          <t>1642867</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1534228</t>
+          <t>1631279</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1554131</t>
+          <t>1652198</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1004348</t>
+          <t>878332</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>994306</t>
+          <t>866783</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1012417</t>
+          <t>886020</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2549897</t>
+          <t>2521200</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2536440</t>
+          <t>2505357</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2563444</t>
+          <t>2533032</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1018444</t>
+          <t>897707</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1018444</t>
+          <t>897707</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1018444</t>
+          <t>897707</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2591981</t>
+          <t>2571010</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2591981</t>
+          <t>2571010</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2591981</t>
+          <t>2571010</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
